--- a/dist/progress-tracker.xlsx
+++ b/dist/progress-tracker.xlsx
@@ -17623,7 +17623,7 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>Ron Larson. *Precalculus with Limits*, 2nd ed. Brooks/Cole, Cengage Learning, 2011.</t>
+          <t>Ron Larson and Robert P. Hostetler. *Precalculus with Limits*, 2nd ed. (Pre-AP National Student Edition) Thomson Brooks/Cole, 2009. ISBN 978-0-538-73659-6.</t>
         </is>
       </c>
     </row>
@@ -17647,7 +17647,7 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>git 6614701</t>
+          <t>git b6c7ce7</t>
         </is>
       </c>
     </row>

--- a/dist/progress-tracker.xlsx
+++ b/dist/progress-tracker.xlsx
@@ -17623,7 +17623,7 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>Ron Larson and Robert P. Hostetler. *Precalculus with Limits*, 2nd ed. (Pre-AP National Student Edition) Thomson Brooks/Cole, 2009. ISBN 978-0-538-73659-6.</t>
+          <t>Ron Larson and Robert P. Hostetler. Precalculus with Limits, 2nd ed. (Pre-AP National Student Edition) Thomson Brooks/Cole, 2009. ISBN 978-0-538-73659-6.</t>
         </is>
       </c>
     </row>
@@ -17647,7 +17647,7 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>git b6c7ce7</t>
+          <t>git 3b8bf92</t>
         </is>
       </c>
     </row>
